--- a/GranBlueFantasy_And_OtherCygame_Support_Dll/package/LangMod/CN/Dialog/Drama/Vajra.xlsx
+++ b/GranBlueFantasy_And_OtherCygame_Support_Dll/package/LangMod/CN/Dialog/Drama/Vajra.xlsx
@@ -540,6 +540,21 @@
     <t>*瓦姬拉加入了队伍*</t>
   </si>
   <si>
+    <t>mod_affinity(200)</t>
+  </si>
+  <si>
+    <t>mod_element(DEX,20)</t>
+  </si>
+  <si>
+    <t>mod_element(STR,20)</t>
+  </si>
+  <si>
+    <t>mod_element(END,20)</t>
+  </si>
+  <si>
+    <t>mod_element(CHA,20)</t>
+  </si>
+  <si>
     <t>（ヴァジラはデバフ無効など強力な特性を持つ。難易度を上げたい場合は帰還させられる）</t>
   </si>
   <si>
@@ -547,21 +562,6 @@
   </si>
   <si>
     <t>（瓦姬拉拥有无视负面BUFF等强力属性，如果不想游戏过于轻松，可以将其送回家中。）</t>
-  </si>
-  <si>
-    <t>mod_affinity(200)</t>
-  </si>
-  <si>
-    <t>mod_element(DEX,20)</t>
-  </si>
-  <si>
-    <t>mod_element(STR,20)</t>
-  </si>
-  <si>
-    <t>mod_element(END,20)</t>
-  </si>
-  <si>
-    <t>mod_element(CHA,20)</t>
   </si>
   <si>
     <t>はい…わかりました（戻る気はまったくない）</t>
@@ -1653,8 +1653,6 @@
         <v>16</v>
       </c>
       <c r="E8" s="6"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
       <c r="J8" s="11"/>
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
@@ -2433,21 +2431,15 @@
         <v>122</v>
       </c>
     </row>
-    <row r="74" spans="9:13">
-      <c r="I74" s="3">
-        <v>26</v>
-      </c>
-      <c r="J74" s="3" t="s">
+    <row r="74" spans="5:7">
+      <c r="E74" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F74" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="K74" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="L74" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="M74" s="3" t="s">
-        <v>125</v>
+      <c r="G74" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="75" spans="5:7">
@@ -2455,7 +2447,7 @@
         <v>50</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>19</v>
@@ -2466,7 +2458,7 @@
         <v>50</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>19</v>
@@ -2477,7 +2469,7 @@
         <v>50</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>19</v>
@@ -2488,21 +2480,27 @@
         <v>50</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="79" spans="5:7">
-      <c r="E79" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F79" s="3" t="s">
+    <row r="79" ht="13" customHeight="1" spans="9:13">
+      <c r="I79" s="3">
+        <v>26</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="L79" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="G79" s="3" t="s">
-        <v>19</v>
+      <c r="M79" s="3" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="81" spans="2:13">
